--- a/lessons/chess/excels/remarks_lcs.xlsx
+++ b/lessons/chess/excels/remarks_lcs.xlsx
@@ -602,7 +602,7 @@
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="J62" authorId="0" shapeId="0">

--- a/lessons/chess/excels/remarks_lcs.xlsx
+++ b/lessons/chess/excels/remarks_lcs.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +32,20 @@
     </font>
     <font>
       <name val="Segoe UI Emoji"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,11 +74,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1381,24 +1403,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1419,24 +1423,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1476,7 +1462,6 @@
       <c r="H4" t="n">
         <v>100</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>96.3</v>
       </c>
@@ -1485,7 +1470,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +4px (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +Children (00:00:00), +broder (00:00:00), +broder (00:00:00), +broder (00:00:00), +const (00:00:00), +documnet (00:00:00), +element (00:00:00), +handleClick (00:00:00), +onclick (00:00:00), +red (00:00:00), +replace (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpisce (00:00:00), +solid (00:00:00), +style (00:00:00), +this (00:00:00), -/ (11:54:17.061), -border (12:35:31.651), -document (12:37:53.239), -border (12:45:17.066), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -1497,7 +1481,6 @@
       <c r="O4" t="n">
         <v>100</v>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>74</v>
       </c>
@@ -1506,12 +1489,11 @@
           <t>-border (12:35:31.651), -document (12:37:53.239), -border (12:45:17.066), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +const (00:00:00), +selectedpiece (00:00:00), +documnet (00:00:00), +broder (00:00:00), +selectedpiece (00:00:00), +replace (00:00:00), +Children (00:00:00), +selectedpisce (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +broder (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +broder (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1559,7 +1541,6 @@
           <t>+" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), += (00:00:00), +DOCTYOE (00:00:00), +const (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00), +onclick (00:00:00), +selectedpPiece (00:00:00), +this (00:00:00), -DOCTYPE (11:53:34.288), -handleClick (12:33:15.189), -} (12:33:32.526), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -1571,7 +1552,6 @@
       <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>92.90000000000001</v>
       </c>
@@ -1580,12 +1560,11 @@
           <t>-handleClick (12:33:15.189), -} (12:33:32.526), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -let (12:56:53.102), +const (00:00:00), +selectedpPiece (00:00:00), +handleclick (00:00:00), +hanleclick (00:00:00)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>C1&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1602,22 +1581,6 @@
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1633,24 +1596,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1671,24 +1616,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1741,7 +1668,6 @@
           <t>+! (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +0 (00:00:00), +100 (00:00:00), +4px (00:00:00), +50px (00:00:00), +50px (00:00:00), +50px (00:00:00), +50px (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +\ (00:00:00), +\ (00:00:00), +border (00:00:00), +c (00:00:00), +cell (00:00:00), +cells (00:00:00), +children (00:00:00), +const (00:00:00), +document (00:00:00), +element (00:00:00), +element (00:00:00), +element (00:00:00), +else (00:00:00), +getElementByClassName (00:00:00), +height (00:00:00), +height (00:00:00), +if (00:00:00), +if (00:00:00), +length (00:00:00), +let (00:00:00), +null (00:00:00), +null (00:00:00), +null (00:00:00), +null (00:00:00), +pieces (00:00:00), +png (00:00:00), +red (00:00:00), +replaceChildren (00:00:00), +rook (00:00:00), +selectdPiece (00:00:00), +selectedPeiece (00:00:00), +selectedPiece (00:00:00), +selectedPiece (00:00:00), +selectedPiece (00:00:00), +solid (00:00:00), +style (00:00:00), +width (00:00:00), +{ (00:00:00), +{ (00:00:00), +} (00:00:00), +} (00:00:00), -&lt; (11:57:53.359), -&lt; (11:58:31.329), -/ (11:58:31.581), -div (11:58:32.273), -&gt; (11:58:32.462), -&lt; (11:58:34.148), -div (11:58:34.737), -class (11:58:35.647), -= (11:58:35.832), -" (11:58:35.965), -cell (11:58:36.694), -dark (11:58:37.525), -" (11:58:37.701), -&gt; (11:58:37.856), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -1fr (12:04:39.902), -1fr (12:05:20.402), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -&gt; (12:08:20.903), -&lt; (12:08:20.913), -/ (12:08:20.923), -div (12:08:20.953), -&gt; (12:08:20.963), -&lt; (12:08:20.983), -div (12:08:21.013), -class (12:08:21.073), -= (12:08:21.083), -" (12:08:21.093), -cell (12:08:21.133), -dark (12:08:21.183), -" (12:08:21.193), -&gt; (12:08:21.203), -&lt; (12:08:21.213), -/ (12:08:21.223), -div (12:08:21.253), -&gt; (12:08:21.263), -&lt; (12:08:21.283), -div (12:08:21.313), -class (12:08:21.373), -= (12:08:21.383), -" (12:08:21.393), -cell (12:08:21.433), -light (12:08:21.493), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -" (12:08:22.413), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -" (12:08:24.863), -&gt; (12:08:24.873), -&lt; (12:08:24.883), -/ (12:08:24.893), -div (12:08:24.923), -&gt; (12:08:24.933), -&lt; (12:08:24.963), -div (12:08:24.993), -class (12:08:25.053), -= (12:08:25.063), -" (12:08:25.073), -cell (12:08:25.113), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -dark (12:08:25.473), -" (12:08:25.483), -&gt; (12:08:25.493), -&lt; (12:08:25.503), -/ (12:08:25.513), -div (12:08:25.543), -&gt; (12:08:25.553), -&lt; (12:08:25.573), -div (12:08:25.603), -class (12:08:25.663), -= (12:08:25.673), -" (12:08:25.683), -cell (12:08:25.723), -light (12:08:25.783), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -" (12:08:27.313), -&gt; (12:08:27.323), -&lt; (12:08:27.333), -/ (12:08:27.343), -div (12:08:27.373), -&gt; (12:08:27.383), -&lt; (12:08:27.413), -div (12:08:27.443), -class (12:08:27.503), -= (12:08:27.513), -" (12:08:27.523), -cell (12:08:27.563), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -light (12:08:27.923), -" (12:08:27.933), -&gt; (12:08:27.943), -&lt; (12:08:27.953), -/ (12:08:27.963), -div (12:08:27.993), -&gt; (12:08:28.003), -&lt; (12:08:28.023), -div (12:08:28.053), -class (12:08:28.113), -= (12:08:28.123), -" (12:08:28.133), -cell (12:08:28.173), -dark (12:08:28.223), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -" (12:08:29.763), -&gt; (12:08:29.773), -&lt; (12:08:29.783), -/ (12:08:29.793), -div (12:08:29.823), -&gt; (12:08:29.833), -&lt; (12:08:29.863), -div (12:08:29.893), -class (12:08:29.953), -= (12:08:29.963), -" (12:08:29.973), -cell (12:08:30.013), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -dark (12:08:30.373), -" (12:08:30.383), -&gt; (12:08:30.393), -&lt; (12:08:30.403), -/ (12:08:30.413), -div (12:08:30.443), -&gt; (12:08:30.453), -&lt; (12:08:30.473), -div (12:08:30.503), -class (12:08:30.563), -= (12:08:30.573), -" (12:08:30.583), -cell (12:08:30.623), -light (12:08:30.683), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -" (12:08:32.213), -&gt; (12:08:32.223), -&lt; (12:08:32.233), -/ (12:08:32.243), -div (12:08:32.273), -&gt; (12:08:32.283), -&lt; (12:08:32.313), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -/ (12:16:05.559), -p2 (12:16:05.801), -&gt; (12:16:07.243), -} (12:17:44.771), -50 (12:20:14.705), -display (12:24:00.258), -flex (12:24:01.038), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -&gt; (12:25:38.438), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -) (12:27:05.426), -} (12:33:32.526), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>19</v>
       </c>
@@ -1766,12 +1692,11 @@
           <t>-} (12:33:32.526), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +) (00:00:00), +; (00:00:00), +let (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +const (00:00:00), +cells (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +cell (00:00:00), +" (00:00:00), +if (00:00:00), +( (00:00:00), +selectedPiece (00:00:00), +! (00:00:00), += (00:00:00), +null (00:00:00), +) (00:00:00), +{ (00:00:00), +element (00:00:00), +. (00:00:00), +replaceChildren (00:00:00), +( (00:00:00), +selectdPiece (00:00:00), +) (00:00:00), +; (00:00:00), +selectedPiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +if (00:00:00), +( (00:00:00), +element (00:00:00), +. (00:00:00), +children (00:00:00), +. (00:00:00), +length (00:00:00), +&gt; (00:00:00), +0 (00:00:00), +) (00:00:00), +{ (00:00:00), +selectedPeiece (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1787,24 +1712,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1825,24 +1732,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1882,7 +1771,6 @@
       <c r="H12" t="n">
         <v>100</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>99.09999999999999</v>
       </c>
@@ -1891,7 +1779,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), += (00:00:00), +handleClick (00:00:00), +onclick (00:00:00), +this (00:00:00), -/ (11:54:17.061)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -1903,17 +1790,14 @@
       <c r="O12" t="n">
         <v>100</v>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1929,24 +1813,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1968,22 +1834,6 @@
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1999,24 +1849,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2037,24 +1869,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2075,24 +1889,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2113,24 +1909,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2183,7 +1961,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +- (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +boder (00:00:00), +class (00:00:00), +color (00:00:00), +handleClick (00:00:00), +invert (00:00:00), +onclick (00:00:00), +this (00:00:00), -" (12:25:37.915), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -border (12:35:31.651), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>97.5</v>
       </c>
@@ -2195,7 +1972,6 @@
       <c r="O19" t="n">
         <v>100</v>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
         <v>94.5</v>
       </c>
@@ -2204,12 +1980,11 @@
           <t>-border (12:35:31.651), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -let (12:56:53.102), +boder (00:00:00)</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2225,24 +2000,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2324,12 +2081,11 @@
           <t>+element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2345,24 +2101,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2383,24 +2121,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2461,7 +2181,6 @@
       <c r="M24" t="n">
         <v>100</v>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>98.2</v>
       </c>
@@ -2478,12 +2197,11 @@
           <t>-} (12:33:32.526), -; (12:52:27.519), +} (00:00:00)</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2560,12 +2278,11 @@
           <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -length (12:53:25.380), -selectedPiece (12:53:29.626), -let (12:56:53.102), +const (00:00:00), +selectedpice (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +lenght (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2581,24 +2298,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2619,24 +2318,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2658,22 +2339,6 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2689,24 +2354,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2746,7 +2393,6 @@
       <c r="H30" t="n">
         <v>100</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>98</v>
       </c>
@@ -2755,7 +2401,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), += (00:00:00), +dispaly (00:00:00), +handleclick (00:00:00), +onclick (00:00:00), +this (00:00:00), -display (12:04:30.837), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>99</v>
       </c>
@@ -2775,13 +2420,11 @@
       <c r="Q30" t="n">
         <v>100</v>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr">
+      <c r="S30" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2845,7 +2488,6 @@
       <c r="O31" t="n">
         <v>100</v>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>61.4</v>
       </c>
@@ -2854,12 +2496,11 @@
           <t>-} (12:33:32.526), -cells (12:38:41.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +element (00:00:00)</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2875,24 +2516,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2913,24 +2536,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2951,24 +2556,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2989,24 +2576,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3046,7 +2615,6 @@
       <c r="H36" t="n">
         <v>100</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>57.9</v>
       </c>
@@ -3055,7 +2623,6 @@
           <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +50 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), += (00:00:00), +chess (00:00:00), +coloumns (00:00:00), +getElement (00:00:00), +handleClick (00:00:00), +height (00:00:00), +onClick (00:00:00), +onclick (00:00:00), +sBYClassName (00:00:00), +this (00:00:00), -Chess (11:54:35.668), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -&gt; (12:25:38.438), -" (12:26:40.406), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -) (12:27:05.426), -} (12:33:32.526), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>55.6</v>
       </c>
@@ -3080,12 +2647,11 @@
           <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00)</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>C2&lt;</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3101,24 +2667,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3139,24 +2687,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3177,24 +2707,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3215,24 +2727,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3254,22 +2748,6 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3286,22 +2764,6 @@
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3317,24 +2779,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3355,24 +2799,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3425,7 +2851,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +cell (00:00:00), +const (00:00:00), +handleClick (00:00:00), +onclick (00:00:00), +this (00:00:00), -cells (12:45:13.133), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>99</v>
       </c>
@@ -3437,7 +2862,6 @@
       <c r="O45" t="n">
         <v>100</v>
       </c>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
         <v>96.09999999999999</v>
       </c>
@@ -3446,12 +2870,11 @@
           <t>-cells (12:45:13.133), -let (12:56:53.102), +const (00:00:00), +cell (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S45" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3499,7 +2922,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), += (00:00:00), +DOCTYOE (00:00:00), +console (00:00:00), +handleClick (00:00:00), +log (00:00:00), +onclick (00:00:00), +this (00:00:00), -DOCTYPE (11:53:34.288), -&gt; (11:58:37.856), -; (12:02:09.908), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -} (12:33:32.526), -const (12:37:48.715), -cells (12:37:50.791), -= (12:37:51.741), -document (12:37:53.239), -. (12:37:53.353), -getElementsByClassName (12:37:56.278), -( (12:37:56.528), -" (12:37:56.625), -cell (12:37:57.315), -" (12:37:57.342), -) (12:37:57.421), -; (12:37:57.967), -console (12:38:39.938), -. (12:38:40.020), -log (12:38:40.505), -( (12:38:40.640), -cells (12:38:41.433), -) (12:38:41.626), -; (12:38:41.842), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>96.7</v>
       </c>
@@ -3524,12 +2946,11 @@
           <t>-} (12:33:32.526), -const (12:37:48.715), -cells (12:37:50.791), -= (12:37:51.741), -document (12:37:53.239), -. (12:37:53.353), -getElementsByClassName (12:37:56.278), -( (12:37:56.528), -" (12:37:56.625), -cell (12:37:57.315), -" (12:37:57.342), -) (12:37:57.421), -; (12:37:57.967), -console (12:38:39.938), -. (12:38:40.020), -log (12:38:40.505), -( (12:38:40.640), -cells (12:38:41.433), -) (12:38:41.626), -; (12:38:41.842), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102), +console (00:00:00), +log (00:00:00)</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>C1&lt;</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3546,22 +2967,6 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3609,7 +3014,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +cell (00:00:00), +chess (00:00:00), +class (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +handleclick (00:00:00), +head (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +light (00:00:00), +onclick (00:00:00), +style (00:00:00), +this (00:00:00), -Chess (11:56:36.040), -/ (11:56:37.399), -dark (11:58:37.525), -; (12:02:09.908), -dark (12:08:25.473), -dark (12:08:30.373), -dark (12:08:35.273), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -) (12:52:12.282), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>94.5</v>
       </c>
@@ -3634,12 +3038,11 @@
           <t>-selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -) (12:52:12.282), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S48" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3655,24 +3058,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3725,7 +3110,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +4px (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +border (00:00:00), +cell (00:00:00), +cells (00:00:00), +console (00:00:00), +const (00:00:00), +element (00:00:00), +element (00:00:00), +element (00:00:00), +for (00:00:00), +function (00:00:00), +getElementaryByClassName (00:00:00), +handClick (00:00:00), +handleClick (00:00:00), +htm (00:00:00), +log (00:00:00), +of (00:00:00), +onclick (00:00:00), +red (00:00:00), +selectededPiece (00:00:00), +solid (00:00:00), +style (00:00:00), +this (00:00:00), +{ (00:00:00), +{ (00:00:00), -html (11:53:51.658), -&lt; (11:57:53.359), -div (12:08:32.343), -class (12:08:32.403), -= (12:08:32.413), -" (12:08:32.423), -cell (12:08:32.463), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -light (12:08:32.823), -" (12:08:32.833), -&gt; (12:08:32.843), -&lt; (12:08:32.853), -/ (12:08:32.863), -div (12:08:32.893), -&gt; (12:08:32.903), -&lt; (12:08:32.923), -div (12:08:32.953), -class (12:08:33.013), -= (12:08:33.023), -" (12:08:33.033), -cell (12:08:33.073), -dark (12:08:33.123), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -" (12:08:34.663), -&gt; (12:08:34.673), -&lt; (12:08:34.683), -/ (12:08:34.693), -div (12:08:34.723), -&gt; (12:08:34.733), -&lt; (12:08:34.763), -div (12:08:34.793), -class (12:08:34.853), -= (12:08:34.863), -" (12:08:34.873), -cell (12:08:34.913), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -dark (12:08:35.273), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -" (12:08:39.563), -&gt; (12:08:39.573), -&lt; (12:08:39.583), -/ (12:08:39.593), -div (12:08:39.623), -&gt; (12:08:39.633), -function (12:33:12.903), -handleClick (12:33:15.189), -( (12:33:15.589), -element (12:33:31.280), -) (12:33:31.506), -{ (12:33:31.963), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>65.5</v>
       </c>
@@ -3737,7 +3121,6 @@
       <c r="O50" t="n">
         <v>100</v>
       </c>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
         <v>43.3</v>
       </c>
@@ -3746,12 +3129,11 @@
           <t>-function (12:33:12.903), -handleClick (12:33:15.189), -( (12:33:15.589), -element (12:33:31.280), -) (12:33:31.506), -{ (12:33:31.963), -getElementsByClassName (12:37:56.278), -for (12:40:04.800), -( (12:40:05.203), -const (12:40:06.186), -cell (12:40:07.141), -of (12:40:07.700), -cells (12:40:08.982), -) (12:40:09.100), -{ (12:40:09.697), -} (12:40:10.504), -cell (12:41:01.994), -. (12:41:02.157), -onclick (12:41:03.120), -= (12:41:03.570), -handleClick (12:41:05.134), -( (12:41:05.326), -cell (12:41:05.940), -) (12:41:06.025), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -; (12:42:56.119), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:53:29.626), -let (12:56:53.102), +getElementaryByClassName (00:00:00), +selectededPiece (00:00:00), +function (00:00:00), +handleClick (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +const (00:00:00), +cell (00:00:00), +of (00:00:00), +cells (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +element (00:00:00), +) (00:00:00), +; (00:00:00), +element (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +border (00:00:00), += (00:00:00), +" (00:00:00), +4px (00:00:00), +solid (00:00:00), +red (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3786,7 +3168,6 @@
       <c r="H51" t="n">
         <v>100</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>99.2</v>
       </c>
@@ -3795,7 +3176,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), += (00:00:00), +handleClick (00:00:00), +onclick (00:00:00), +this (00:00:00)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>99</v>
       </c>
@@ -3807,17 +3187,14 @@
       <c r="O51" t="n">
         <v>100</v>
       </c>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
         <v>100</v>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr">
+      <c r="S51" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3833,24 +3210,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3871,24 +3230,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3909,24 +3250,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3947,24 +3270,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4017,7 +3322,6 @@
           <t>+" (00:00:00), +" (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +const (00:00:00), +heal (00:00:00), +img (00:00:00), +p6 (00:00:00), +pieces (00:00:00), +png (00:00:00), +src (00:00:00), -head (11:54:17.814), -/ (11:57:53.708), -div (11:57:54.317), -&gt; (11:57:54.617), -&lt; (12:32:49.891), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>98</v>
       </c>
@@ -4029,7 +3333,6 @@
       <c r="O56" t="n">
         <v>100</v>
       </c>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
         <v>98.40000000000001</v>
       </c>
@@ -4038,12 +3341,11 @@
           <t>-let (12:56:53.102), +const (00:00:00)</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4059,24 +3361,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4097,24 +3381,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4167,7 +3433,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +% (00:00:00), +% (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +100 (00:00:00), +2px (00:00:00), +50 (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +anonymous (00:00:00), +border (00:00:00), +cell (00:00:00), +cell (00:00:00), +cell (00:00:00), +class (00:00:00), +class (00:00:00), +color (00:00:00), +console (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +element (00:00:00), +filter (00:00:00), +function (00:00:00), +handleclick (00:00:00), +ing (00:00:00), +invert (00:00:00), +invert (00:00:00), +light (00:00:00), +long (00:00:00), +solid (00:00:00), +width (00:00:00), +{ (00:00:00), +{ (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), -! (11:53:33.047), -&lt; (12:01:45.480), -/ (12:01:45.692), -style (12:01:46.591), -&gt; (12:01:46.854), -} (12:02:03.928), -; (12:02:47.484), -; (12:02:56.888), -dark (12:08:22.713), -" (12:08:22.723), -&gt; (12:08:22.733), -&lt; (12:08:22.743), -/ (12:08:22.753), -div (12:08:22.783), -&gt; (12:08:22.793), -&lt; (12:08:22.813), -div (12:08:22.843), -class (12:08:22.903), -= (12:08:22.913), -" (12:08:22.923), -cell (12:08:22.963), -" (12:08:23.333), -&gt; (12:08:23.343), -&lt; (12:08:23.353), -/ (12:08:23.363), -div (12:08:23.393), -&gt; (12:08:23.403), -&lt; (12:08:23.423), -div (12:08:23.453), -class (12:08:23.513), -= (12:08:23.523), -" (12:08:23.533), -cell (12:08:23.573), -light (12:08:23.633), -" (12:08:23.643), -&gt; (12:08:23.653), -&lt; (12:08:23.663), -/ (12:08:23.673), -div (12:08:23.703), -&gt; (12:08:23.713), -&lt; (12:08:23.733), -div (12:08:23.763), -class (12:08:23.823), -= (12:08:23.833), -" (12:08:23.843), -cell (12:08:23.883), -dark (12:08:23.933), -" (12:08:23.943), -&gt; (12:08:23.953), -&lt; (12:08:23.963), -/ (12:08:23.973), -div (12:08:24.003), -&gt; (12:08:24.013), -&lt; (12:08:24.033), -div (12:08:24.063), -class (12:08:24.123), -= (12:08:24.133), -" (12:08:24.143), -cell (12:08:24.183), -light (12:08:24.243), -" (12:08:24.253), -&gt; (12:08:24.263), -&lt; (12:08:24.273), -/ (12:08:24.283), -div (12:08:24.313), -&gt; (12:08:24.323), -&lt; (12:08:24.343), -div (12:08:24.373), -class (12:08:24.433), -= (12:08:24.443), -" (12:08:24.453), -cell (12:08:24.493), -dark (12:08:24.543), -" (12:08:24.553), -&gt; (12:08:24.563), -&lt; (12:08:24.573), -/ (12:08:24.583), -div (12:08:24.613), -&gt; (12:08:24.623), -&lt; (12:08:24.643), -div (12:08:24.673), -class (12:08:24.733), -= (12:08:24.743), -" (12:08:24.753), -cell (12:08:24.793), -light (12:08:24.853), -dark (12:08:27.613), -" (12:08:27.623), -&gt; (12:08:27.633), -&lt; (12:08:27.643), -/ (12:08:27.653), -div (12:08:27.683), -&gt; (12:08:27.693), -&lt; (12:08:27.713), -div (12:08:27.743), -class (12:08:27.803), -= (12:08:27.813), -" (12:08:27.823), -cell (12:08:27.863), -" (12:08:28.233), -&gt; (12:08:28.243), -&lt; (12:08:28.253), -/ (12:08:28.263), -div (12:08:28.293), -&gt; (12:08:28.303), -&lt; (12:08:28.323), -div (12:08:28.353), -class (12:08:28.413), -= (12:08:28.423), -" (12:08:28.433), -cell (12:08:28.473), -light (12:08:28.533), -" (12:08:28.543), -&gt; (12:08:28.553), -&lt; (12:08:28.563), -/ (12:08:28.573), -div (12:08:28.603), -&gt; (12:08:28.613), -&lt; (12:08:28.633), -div (12:08:28.663), -class (12:08:28.723), -= (12:08:28.733), -" (12:08:28.743), -cell (12:08:28.783), -dark (12:08:28.833), -" (12:08:28.843), -&gt; (12:08:28.853), -&lt; (12:08:28.863), -/ (12:08:28.873), -div (12:08:28.903), -&gt; (12:08:28.913), -&lt; (12:08:28.933), -div (12:08:28.963), -class (12:08:29.023), -= (12:08:29.033), -" (12:08:29.043), -cell (12:08:29.083), -light (12:08:29.143), -" (12:08:29.153), -&gt; (12:08:29.163), -&lt; (12:08:29.173), -/ (12:08:29.183), -div (12:08:29.213), -&gt; (12:08:29.223), -&lt; (12:08:29.243), -div (12:08:29.273), -class (12:08:29.333), -= (12:08:29.343), -" (12:08:29.353), -cell (12:08:29.393), -dark (12:08:29.443), -" (12:08:29.453), -&gt; (12:08:29.463), -&lt; (12:08:29.473), -/ (12:08:29.483), -div (12:08:29.513), -&gt; (12:08:29.523), -&lt; (12:08:29.543), -div (12:08:29.573), -class (12:08:29.633), -= (12:08:29.643), -" (12:08:29.653), -cell (12:08:29.693), -light (12:08:29.753), -dark (12:08:32.513), -" (12:08:32.523), -&gt; (12:08:32.533), -&lt; (12:08:32.543), -/ (12:08:32.553), -div (12:08:32.583), -&gt; (12:08:32.593), -&lt; (12:08:32.613), -div (12:08:32.643), -class (12:08:32.703), -= (12:08:32.713), -" (12:08:32.723), -cell (12:08:32.763), -" (12:08:33.133), -&gt; (12:08:33.143), -&lt; (12:08:33.153), -/ (12:08:33.163), -div (12:08:33.193), -&gt; (12:08:33.203), -&lt; (12:08:33.223), -div (12:08:33.253), -class (12:08:33.313), -= (12:08:33.323), -" (12:08:33.333), -cell (12:08:33.373), -light (12:08:33.433), -" (12:08:33.443), -&gt; (12:08:33.453), -&lt; (12:08:33.463), -/ (12:08:33.473), -div (12:08:33.503), -&gt; (12:08:33.513), -&lt; (12:08:33.533), -div (12:08:33.563), -class (12:08:33.623), -= (12:08:33.633), -" (12:08:33.643), -cell (12:08:33.683), -dark (12:08:33.733), -" (12:08:33.743), -&gt; (12:08:33.753), -&lt; (12:08:33.763), -/ (12:08:33.773), -div (12:08:33.803), -&gt; (12:08:33.813), -&lt; (12:08:33.833), -div (12:08:33.863), -class (12:08:33.923), -= (12:08:33.933), -" (12:08:33.943), -cell (12:08:33.983), -light (12:08:34.043), -" (12:08:34.053), -&gt; (12:08:34.063), -&lt; (12:08:34.073), -/ (12:08:34.083), -div (12:08:34.113), -&gt; (12:08:34.123), -&lt; (12:08:34.143), -div (12:08:34.173), -class (12:08:34.233), -= (12:08:34.243), -" (12:08:34.253), -cell (12:08:34.293), -dark (12:08:34.343), -" (12:08:34.353), -&gt; (12:08:34.363), -&lt; (12:08:34.373), -/ (12:08:34.383), -div (12:08:34.413), -&gt; (12:08:34.423), -&lt; (12:08:34.443), -div (12:08:34.473), -class (12:08:34.533), -= (12:08:34.543), -" (12:08:34.553), -cell (12:08:34.593), -light (12:08:34.653), -img (12:17:42.332), -{ (12:17:43.944), -} (12:17:44.771), -width (12:17:46.547), -: (12:17:46.642), -50 (12:20:14.705), -% (12:20:15.067), -; (12:20:15.756), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -} (12:33:32.526), -for (12:45:10.759), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>72.09999999999999</v>
       </c>
@@ -4192,12 +3457,11 @@
           <t>-} (12:33:32.526), -for (12:45:10.759), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -{ (12:45:13.433), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -( (12:53:21.914), -element (12:53:22.881), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -) (12:53:26.161), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -; (12:53:33.056), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S59" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4213,24 +3477,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4252,22 +3498,6 @@
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4291,14 +3521,12 @@
       <c r="E62" t="n">
         <v>0</v>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>99.7</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
         <v>99.7</v>
       </c>
@@ -4323,7 +3551,6 @@
       <c r="O62" t="n">
         <v>100</v>
       </c>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>99.2</v>
       </c>
@@ -4332,12 +3559,11 @@
           <t>-; (12:42:56.119)</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S62" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4353,24 +3579,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4391,24 +3599,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4429,24 +3619,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4499,7 +3671,6 @@
           <t>+DOCTYOE (00:00:00), +const (00:00:00), +selectedpiece (00:00:00), -DOCTYPE (11:53:34.288), -&gt; (11:58:37.856), -; (12:02:09.908), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -} (12:33:32.526), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -selectedPiece (12:52:11.048), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>97.7</v>
       </c>
@@ -4524,12 +3695,11 @@
           <t>-} (12:33:32.526), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -selectedPiece (12:52:11.048), -let (12:56:53.102), +const (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr">
+        <is>
+          <t>C1&lt;</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4545,24 +3715,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4615,7 +3767,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +# (00:00:00), +( (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +- (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +1fr (00:00:00), +1fr (00:00:00), +400px (00:00:00), +400px (00:00:00), +60 (00:00:00), +8 (00:00:00), +8 (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Game (00:00:00), +black (00:00:00), +board (00:00:00), +board (00:00:00), +cell (00:00:00), +chess (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +class (00:00:00), +columns (00:00:00), +dark (00:00:00), +display (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +getElementById (00:00:00), +grey (00:00:00), +grid (00:00:00), +grid (00:00:00), +grid (00:00:00), +handleClick (00:00:00), +height (00:00:00), +onclick (00:00:00), +repeat (00:00:00), +repeat (00:00:00), +replaceChild (00:00:00), +return (00:00:00), +row (00:00:00), +row (00:00:00), +row (00:00:00), +row (00:00:00), +row (00:00:00), +row (00:00:00), +row (00:00:00), +row (00:00:00), +rows (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00), +template (00:00:00), +template (00:00:00), +this (00:00:00), +this (00:00:00), +width (00:00:00), +{ (00:00:00), +} (00:00:00), -&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -/ (11:58:31.581), -dark (11:58:37.525), -} (12:02:52.276), -gray (12:02:56.667), -; (12:02:56.888), -# (12:03:33.003), -chess (12:03:34.679), -- (12:03:34.891), -board (12:03:35.921), -{ (12:03:45.639), -width (12:03:53.681), -: (12:03:53.818), -400px (12:03:55.740), -; (12:03:56.458), -height (12:03:58.438), -: (12:03:58.649), -400px (12:03:59.637), -; (12:03:59.993), -display (12:04:30.837), -: (12:04:30.966), -grid (12:04:31.833), -; (12:04:31.971), -grid (12:04:33.784), -- (12:04:33.928), -template (12:04:35.620), -- (12:04:35.828), -rows (12:04:36.631), -: (12:04:36.826), -repeat (12:04:38.281), -( (12:04:38.485), -8 (12:04:38.643), -, (12:04:38.821), -1fr (12:04:39.902), -) (12:04:40.295), -; (12:04:41.132), -grid (12:05:13.862), -- (12:05:13.980), -template (12:05:15.274), -- (12:05:15.459), -columns (12:05:17.007), -: (12:05:17.574), -repeat (12:05:19.260), -( (12:05:19.386), -8 (12:05:19.565), -, (12:05:19.720), -1fr (12:05:20.402), -) (12:05:20.749), -} (12:17:44.771), -50 (12:20:14.705), -; (12:20:15.756), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -cells (12:37:50.791), -getElementsByClassName (12:37:56.278), -cell (12:41:05.940), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>85.8</v>
       </c>
@@ -4640,12 +3791,11 @@
           <t>-cells (12:37:50.791), -getElementsByClassName (12:37:56.278), -cell (12:41:05.940), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +board (00:00:00), +getElementById (00:00:00), +this (00:00:00), +selectedpice (00:00:00), += (00:00:00), +replaceChild (00:00:00), +selectedpice (00:00:00), +selectedpice (00:00:00), +selectedpiece (00:00:00), +return (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4661,24 +3811,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4731,7 +3863,6 @@
           <t>+" (00:00:00), +" (00:00:00), +' (00:00:00), +( (00:00:00), +) (00:00:00), +/ (00:00:00), +/ (00:00:00), +1 (00:00:00), +50 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), += (00:00:00), +chess (00:00:00), +coloumns (00:00:00), +const (00:00:00), +fraction (00:00:00), +getElement (00:00:00), +handleClick (00:00:00), +height (00:00:00), +onClick (00:00:00), +onclick (00:00:00), +replaceChirldren (00:00:00), +sBYClassName (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +this (00:00:00), -Chess (11:54:35.668), -&lt; (11:58:38.260), -/ (11:58:38.465), -div (11:58:38.988), -&gt; (11:58:39.110), -; (12:02:47.484), -; (12:02:56.888), -columns (12:05:17.007), -&lt; (12:08:20.673), -div (12:08:20.703), -class (12:08:20.763), -= (12:08:20.773), -" (12:08:20.783), -cell (12:08:20.823), -light (12:08:20.883), -" (12:08:20.893), -" (12:08:21.503), -&gt; (12:08:21.513), -&lt; (12:08:21.523), -/ (12:08:21.533), -div (12:08:21.563), -&gt; (12:08:21.573), -&lt; (12:08:21.593), -div (12:08:21.623), -class (12:08:21.683), -= (12:08:21.693), -" (12:08:21.703), -cell (12:08:21.743), -dark (12:08:21.793), -" (12:08:21.803), -&gt; (12:08:21.813), -&lt; (12:08:21.823), -/ (12:08:21.833), -div (12:08:21.863), -&gt; (12:08:21.873), -&lt; (12:08:21.893), -div (12:08:21.923), -class (12:08:21.983), -= (12:08:21.993), -" (12:08:22.003), -cell (12:08:22.043), -light (12:08:22.103), -" (12:08:22.113), -&gt; (12:08:22.123), -&lt; (12:08:22.133), -/ (12:08:22.143), -div (12:08:22.173), -&gt; (12:08:22.183), -&lt; (12:08:22.203), -div (12:08:22.233), -class (12:08:22.293), -= (12:08:22.303), -" (12:08:22.313), -cell (12:08:22.353), -dark (12:08:22.403), -light (12:08:25.173), -" (12:08:25.183), -&gt; (12:08:25.193), -&lt; (12:08:25.203), -/ (12:08:25.213), -div (12:08:25.243), -&gt; (12:08:25.253), -&lt; (12:08:25.273), -div (12:08:25.303), -class (12:08:25.363), -= (12:08:25.373), -" (12:08:25.383), -cell (12:08:25.423), -" (12:08:25.793), -&gt; (12:08:25.803), -&lt; (12:08:25.813), -/ (12:08:25.823), -div (12:08:25.853), -&gt; (12:08:25.863), -&lt; (12:08:25.883), -div (12:08:25.913), -class (12:08:25.973), -= (12:08:25.983), -" (12:08:25.993), -cell (12:08:26.033), -dark (12:08:26.083), -" (12:08:26.093), -&gt; (12:08:26.103), -&lt; (12:08:26.113), -/ (12:08:26.123), -div (12:08:26.153), -&gt; (12:08:26.163), -&lt; (12:08:26.183), -div (12:08:26.213), -class (12:08:26.273), -= (12:08:26.283), -" (12:08:26.293), -cell (12:08:26.333), -light (12:08:26.393), -" (12:08:26.403), -&gt; (12:08:26.413), -&lt; (12:08:26.423), -/ (12:08:26.433), -div (12:08:26.463), -&gt; (12:08:26.473), -&lt; (12:08:26.493), -div (12:08:26.523), -class (12:08:26.583), -= (12:08:26.593), -" (12:08:26.603), -cell (12:08:26.643), -dark (12:08:26.693), -" (12:08:26.703), -&gt; (12:08:26.713), -&lt; (12:08:26.723), -/ (12:08:26.733), -div (12:08:26.763), -&gt; (12:08:26.773), -&lt; (12:08:26.793), -div (12:08:26.823), -class (12:08:26.883), -= (12:08:26.893), -" (12:08:26.903), -cell (12:08:26.943), -light (12:08:27.003), -" (12:08:27.013), -&gt; (12:08:27.023), -&lt; (12:08:27.033), -/ (12:08:27.043), -div (12:08:27.073), -&gt; (12:08:27.083), -&lt; (12:08:27.103), -div (12:08:27.133), -class (12:08:27.193), -= (12:08:27.203), -" (12:08:27.213), -cell (12:08:27.253), -dark (12:08:27.303), -light (12:08:30.073), -" (12:08:30.083), -&gt; (12:08:30.093), -&lt; (12:08:30.103), -/ (12:08:30.113), -div (12:08:30.143), -&gt; (12:08:30.153), -&lt; (12:08:30.173), -div (12:08:30.203), -class (12:08:30.263), -= (12:08:30.273), -" (12:08:30.283), -cell (12:08:30.323), -" (12:08:30.693), -&gt; (12:08:30.703), -&lt; (12:08:30.713), -/ (12:08:30.723), -div (12:08:30.753), -&gt; (12:08:30.763), -&lt; (12:08:30.783), -div (12:08:30.813), -class (12:08:30.873), -= (12:08:30.883), -" (12:08:30.893), -cell (12:08:30.933), -dark (12:08:30.983), -" (12:08:30.993), -&gt; (12:08:31.003), -&lt; (12:08:31.013), -/ (12:08:31.023), -div (12:08:31.053), -&gt; (12:08:31.063), -&lt; (12:08:31.083), -div (12:08:31.113), -class (12:08:31.173), -= (12:08:31.183), -" (12:08:31.193), -cell (12:08:31.233), -light (12:08:31.293), -" (12:08:31.303), -&gt; (12:08:31.313), -&lt; (12:08:31.323), -/ (12:08:31.333), -div (12:08:31.363), -&gt; (12:08:31.373), -&lt; (12:08:31.393), -div (12:08:31.423), -class (12:08:31.483), -= (12:08:31.493), -" (12:08:31.503), -cell (12:08:31.543), -dark (12:08:31.593), -" (12:08:31.603), -&gt; (12:08:31.613), -&lt; (12:08:31.623), -/ (12:08:31.633), -div (12:08:31.663), -&gt; (12:08:31.673), -&lt; (12:08:31.693), -div (12:08:31.723), -class (12:08:31.783), -= (12:08:31.793), -" (12:08:31.803), -cell (12:08:31.843), -light (12:08:31.903), -" (12:08:31.913), -&gt; (12:08:31.923), -&lt; (12:08:31.933), -/ (12:08:31.943), -div (12:08:31.973), -&gt; (12:08:31.983), -&lt; (12:08:32.003), -div (12:08:32.033), -class (12:08:32.093), -= (12:08:32.103), -" (12:08:32.113), -cell (12:08:32.153), -dark (12:08:32.203), -light (12:08:34.973), -" (12:08:34.983), -&gt; (12:08:34.993), -&lt; (12:08:35.003), -/ (12:08:35.013), -div (12:08:35.043), -&gt; (12:08:35.053), -&lt; (12:08:35.073), -div (12:08:35.103), -class (12:08:35.163), -= (12:08:35.173), -" (12:08:35.183), -cell (12:08:35.223), -" (12:08:35.283), -&gt; (12:08:35.293), -&lt; (12:08:35.303), -/ (12:08:35.313), -div (12:08:35.343), -&gt; (12:08:35.353), -&lt; (12:08:35.373), -div (12:08:35.403), -class (12:08:35.463), -= (12:08:35.473), -" (12:08:35.483), -cell (12:08:35.523), -light (12:08:35.583), -" (12:08:35.593), -&gt; (12:08:35.603), -&lt; (12:08:35.613), -/ (12:08:35.623), -div (12:08:35.653), -&gt; (12:08:35.663), -&lt; (12:08:35.683), -div (12:08:35.713), -class (12:08:35.773), -= (12:08:35.783), -" (12:08:35.793), -cell (12:08:35.833), -dark (12:08:35.883), -" (12:08:35.893), -&gt; (12:08:35.903), -&lt; (12:08:35.913), -/ (12:08:35.923), -div (12:08:35.953), -&gt; (12:08:35.963), -&lt; (12:08:35.983), -div (12:08:36.013), -class (12:08:36.073), -= (12:08:36.083), -" (12:08:36.093), -cell (12:08:36.133), -light (12:08:36.193), -" (12:08:36.203), -&gt; (12:08:36.213), -&lt; (12:08:36.223), -/ (12:08:36.233), -div (12:08:36.263), -&gt; (12:08:36.273), -&lt; (12:08:36.293), -div (12:08:36.323), -class (12:08:36.383), -= (12:08:36.393), -" (12:08:36.403), -cell (12:08:36.443), -dark (12:08:36.493), -" (12:08:36.503), -&gt; (12:08:36.513), -&lt; (12:08:36.523), -/ (12:08:36.533), -div (12:08:36.563), -&gt; (12:08:36.573), -&lt; (12:08:36.593), -div (12:08:36.623), -class (12:08:36.683), -= (12:08:36.693), -" (12:08:36.703), -cell (12:08:36.743), -light (12:08:36.803), -" (12:08:36.813), -&gt; (12:08:36.823), -&lt; (12:08:36.833), -/ (12:08:36.843), -div (12:08:36.873), -&gt; (12:08:36.883), -&lt; (12:08:36.903), -div (12:08:36.933), -class (12:08:36.993), -= (12:08:37.003), -" (12:08:37.013), -cell (12:08:37.053), -dark (12:08:37.103), -" (12:08:37.113), -&gt; (12:08:37.123), -&lt; (12:08:37.133), -/ (12:08:37.143), -div (12:08:37.173), -&gt; (12:08:37.183), -&lt; (12:08:37.213), -div (12:08:37.243), -class (12:08:37.303), -= (12:08:37.313), -" (12:08:37.323), -cell (12:08:37.363), -dark (12:08:37.413), -" (12:08:37.423), -&gt; (12:08:37.433), -&lt; (12:08:37.443), -/ (12:08:37.453), -div (12:08:37.483), -&gt; (12:08:37.493), -&lt; (12:08:37.513), -div (12:08:37.543), -class (12:08:37.603), -= (12:08:37.613), -" (12:08:37.623), -cell (12:08:37.663), -light (12:08:37.723), -" (12:08:37.733), -&gt; (12:08:37.743), -&lt; (12:08:37.753), -/ (12:08:37.763), -div (12:08:37.793), -&gt; (12:08:37.803), -&lt; (12:08:37.823), -div (12:08:37.853), -class (12:08:37.913), -= (12:08:37.923), -" (12:08:37.933), -cell (12:08:37.973), -dark (12:08:38.023), -" (12:08:38.033), -&gt; (12:08:38.043), -&lt; (12:08:38.053), -/ (12:08:38.063), -div (12:08:38.093), -&gt; (12:08:38.103), -&lt; (12:08:38.123), -div (12:08:38.153), -class (12:08:38.213), -= (12:08:38.223), -" (12:08:38.233), -cell (12:08:38.273), -light (12:08:38.333), -" (12:08:38.343), -&gt; (12:08:38.353), -&lt; (12:08:38.363), -/ (12:08:38.373), -div (12:08:38.403), -&gt; (12:08:38.413), -&lt; (12:08:38.433), -div (12:08:38.463), -class (12:08:38.523), -= (12:08:38.533), -" (12:08:38.543), -cell (12:08:38.583), -dark (12:08:38.633), -" (12:08:38.643), -&gt; (12:08:38.653), -&lt; (12:08:38.663), -/ (12:08:38.673), -div (12:08:38.703), -&gt; (12:08:38.713), -&lt; (12:08:38.733), -div (12:08:38.763), -class (12:08:38.823), -= (12:08:38.833), -" (12:08:38.843), -cell (12:08:38.883), -light (12:08:38.943), -" (12:08:38.953), -&gt; (12:08:38.963), -&lt; (12:08:38.973), -/ (12:08:38.983), -div (12:08:39.013), -&gt; (12:08:39.023), -&lt; (12:08:39.043), -div (12:08:39.073), -class (12:08:39.133), -= (12:08:39.143), -" (12:08:39.153), -cell (12:08:39.193), -dark (12:08:39.243), -" (12:08:39.253), -&gt; (12:08:39.263), -&lt; (12:08:39.273), -/ (12:08:39.283), -div (12:08:39.313), -&gt; (12:08:39.323), -&lt; (12:08:39.343), -div (12:08:39.373), -class (12:08:39.433), -= (12:08:39.443), -" (12:08:39.453), -cell (12:08:39.493), -light (12:08:39.553), -} (12:17:44.771), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -&gt; (12:25:38.438), -" (12:26:40.406), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -filter (12:27:03.521), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -) (12:27:05.426), -getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>55.6</v>
       </c>
@@ -4756,12 +3887,11 @@
           <t>-getElementsByClassName (12:37:56.278), -onclick (12:41:03.120), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), -let (12:56:53.102), +const (00:00:00), +selectedpiece (00:00:00), +getElement (00:00:00), +sBYClassName (00:00:00), +onClick (00:00:00), +selectedpiece (00:00:00), +replaceChirldren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>C2&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4796,7 +3926,6 @@
       <c r="H71" t="n">
         <v>100</v>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -4805,7 +3934,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), +const (00:00:00), +grey (00:00:00), +handleClick (00:00:00), +onclick (00:00:00), +this (00:00:00), -/ (11:54:54.552), -gray (12:02:56.667), -; (12:05:21.226), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>98.8</v>
       </c>
@@ -4830,12 +3958,11 @@
           <t>-let (12:56:53.102), +const (00:00:00)</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S71" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4883,7 +4010,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +1 (00:00:00), +; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +Children (00:00:00), +Pieces (00:00:00), +anonymous (00:00:00), +cell (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +fraction (00:00:00), +function (00:00:00), +handleClick (00:00:00), +light (00:00:00), +onclick (00:00:00), +this (00:00:00), -dark (11:58:37.525), -; (12:02:09.908), -pieces (12:16:05.490), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -} (12:33:32.526), -children (12:53:24.251)</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>95.90000000000001</v>
       </c>
@@ -4908,12 +4034,11 @@
           <t>-} (12:33:32.526), -children (12:53:24.251)</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S72" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4948,7 +4073,6 @@
       <c r="H73" t="n">
         <v>100</v>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>92.5</v>
       </c>
@@ -4957,7 +4081,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +/ (00:00:00), +/ (00:00:00), +00 (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +\ (00:00:00), +\ (00:00:00), +cell (00:00:00), +cell (00:00:00), +class (00:00:00), +class (00:00:00), +const (00:00:00), +dark (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +div (00:00:00), +eleement (00:00:00), +handClick (00:00:00), +handleclick (00:00:00), +light (00:00:00), +onclick (00:00:00), +this (00:00:00), -&lt; (11:53:50.287), -/ (11:53:50.722), -html (11:53:51.658), -&gt; (11:53:52.247), -&lt; (11:54:54.301), -/ (11:54:54.552), -body (11:54:55.321), -&gt; (11:54:55.640), -; (12:02:09.908), -/ (12:16:05.559), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -/ (12:25:37.107), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), -element (12:33:31.280), -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134), -} (12:53:34.736), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>94.59999999999999</v>
       </c>
@@ -4982,12 +4105,11 @@
           <t>-element (12:33:31.280), -} (12:33:32.526), -element (12:35:29.854), -. (12:35:29.918), -style (12:35:30.684), -. (12:35:30.708), -border (12:35:31.651), -= (12:35:31.979), -" (12:35:32.153), -4px (12:35:32.780), -solid (12:35:33.773), -red (12:35:34.503), -" (12:35:34.724), -; (12:35:34.812), -handleClick (12:41:05.134), -} (12:53:34.736), -let (12:56:53.102), +const (00:00:00), +handClick (00:00:00), +eleement (00:00:00), +00 (00:00:00)</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S73" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5003,24 +4125,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5073,7 +4177,6 @@
           <t>+654321 (00:00:00), +DOCTYOE (00:00:00), +console (00:00:00), +getElementsbyClassName (00:00:00), +handleclick (00:00:00), +log (00:00:00), -DOCTYPE (11:53:34.288), -123456 (11:54:38.411), -&gt; (11:58:37.856), -; (12:02:09.908), -display (12:24:00.258), -: (12:24:00.330), -flex (12:24:01.038), -; (12:24:01.089), -align (12:24:02.090), -- (12:24:02.167), -items (12:24:02.854), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -&lt; (12:25:35.200), -img (12:25:35.614), -src (12:25:36.077), -= (12:25:36.163), -" (12:25:36.284), -pieces (12:25:36.945), -/ (12:25:37.107), -p5 (12:25:37.336), -. (12:25:37.455), -png (12:25:37.839), -" (12:25:37.915), -/ (12:25:38.278), -class (12:26:40.137), -= (12:26:40.349), -" (12:26:40.406), -invert (12:26:41.264), -- (12:26:41.305), -color (12:26:42.154), -" (12:26:42.352), -. (12:26:59.213), -invert (12:27:00.293), -- (12:27:00.514), -color (12:27:01.097), -{ (12:27:01.630), -} (12:27:01.824), -filter (12:27:03.521), -: (12:27:03.624), -invert (12:27:04.621), -( (12:27:04.730), -100 (12:27:05.245), -% (12:27:05.347), -) (12:27:05.426), -; (12:27:05.639), -&lt; (12:32:56.391), -/ (12:32:56.665), -script (12:32:57.709), -&gt; (12:32:57.900), -} (12:33:32.526), -getElementsByClassName (12:37:56.278), -handleClick (12:41:05.134), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>97</v>
       </c>
@@ -5098,12 +4201,11 @@
           <t>-} (12:33:32.526), -getElementsByClassName (12:37:56.278), -handleClick (12:41:05.134), -; (12:41:06.130), -function (12:42:53.629), -( (12:42:53.778), -) (12:42:54.059), -{ (12:42:54.497), -} (12:42:55.817), -for (12:45:10.759), -( (12:45:10.951), -const (12:45:11.606), -cell (12:45:12.088), -of (12:45:12.446), -cells (12:45:13.133), -) (12:45:13.304), -{ (12:45:13.433), -} (12:45:14.115), -cell (12:45:15.612), -style (12:45:16.268), -. (12:45:16.371), -border (12:45:17.066), -= (12:45:17.426), -" (12:45:17.580), -" (12:45:17.718), -; (12:45:17.816), -selectedPiece (12:51:24.571), -= (12:51:25.051), -null (12:51:25.997), -; (12:51:26.172), -if (12:52:09.187), -( (12:52:09.526), -selectedPiece (12:52:11.048), -! (12:52:11.221), -= (12:52:11.422), -null (12:52:12.167), -) (12:52:12.282), -{ (12:52:13.202), -} (12:52:13.907), -element (12:52:17.350), -. (12:52:17.520), -replaceChildren (12:52:19.891), -( (12:52:20.134), -selectedPiece (12:52:27.102), -) (12:52:27.322), -; (12:52:27.519), -selectedPiece (12:52:30.641), -= (12:52:30.798), -null (12:52:31.700), -; (12:52:31.752), -else (12:53:21.083), -if (12:53:21.591), -. (12:53:23.171), -children (12:53:24.251), -. (12:53:24.441), -length (12:53:25.380), -&gt; (12:53:25.564), -0 (12:53:25.976), -{ (12:53:26.816), -selectedPiece (12:53:29.626), -= (12:53:29.829), -element (12:53:30.892), -. (12:53:31.019), -children (12:53:32.216), -[ (12:53:32.444), -0 (12:53:32.513), -] (12:53:32.598), -let (12:56:53.102), +getElementsbyClassName (00:00:00), +handleclick (00:00:00), +console (00:00:00), +log (00:00:00)</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr"/>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>C1&lt;</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5119,24 +4221,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5157,24 +4241,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5214,7 +4280,6 @@
       <c r="H78" t="n">
         <v>100</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>96.5</v>
       </c>
@@ -5223,7 +4288,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), += (00:00:00), +chess (00:00:00), +chess (00:00:00), +game (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +onclick (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +this (00:00:00), +} (00:00:00), -Chess (11:54:35.668), -Chess (11:56:36.040), -Game (11:56:37.110), -} (12:02:03.928), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -: (12:24:06.199), -center (12:24:07.000), -; (12:24:07.221), -handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>98.40000000000001</v>
       </c>
@@ -5248,12 +4312,11 @@
           <t>-handleClick (12:33:15.189), -handleClick (12:41:05.134), -selectedPiece (12:51:24.571), -selectedPiece (12:52:11.048), -replaceChildren (12:52:19.891), -selectedPiece (12:52:27.102), -selectedPiece (12:52:30.641), -selectedPiece (12:53:29.626), +selectedpiece (00:00:00), +handleclick (00:00:00), +handleclick (00:00:00), +selectedpiece (00:00:00), +replacechildren (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00), +selectedpiece (00:00:00)</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S78" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5277,37 +4340,29 @@
       <c r="E79" t="n">
         <v>0</v>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>100</v>
       </c>
       <c r="H79" t="n">
         <v>100</v>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
         <v>100</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>100</v>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>100</v>
       </c>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
         <v>100</v>
       </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr">
+      <c r="S79" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5323,24 +4378,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5417,13 +4454,11 @@
       <c r="Q81" t="n">
         <v>100</v>
       </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr">
+      <c r="S81" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5471,7 +4506,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +% (00:00:00), +( (00:00:00), +) (00:00:00), +- (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +50 (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +center (00:00:00), +content (00:00:00), +handleClick (00:00:00), +img (00:00:00), +img (00:00:00), +img (00:00:00), +img (00:00:00), +img (00:00:00), +img (00:00:00), +img (00:00:00), +justify (00:00:00), +onclick (00:00:00), +p2 (00:00:00), +p3 (00:00:00), +p4 (00:00:00), +p5 (00:00:00), +p6 (00:00:00), +p6 (00:00:00), +pieces (00:00:00), +pieces (00:00:00), +pieces (00:00:00), +pieces (00:00:00), +pieces (00:00:00), +pieces (00:00:00), +png (00:00:00), +png (00:00:00), +png (00:00:00), +png (00:00:00), +png (00:00:00), +png (00:00:00), +src (00:00:00), +src (00:00:00), +src (00:00:00), +src (00:00:00), +src (00:00:00), +src (00:00:00), +this (00:00:00), +width (00:00:00), +{ (00:00:00), +} (00:00:00), -} (12:03:46.236), -; (12:05:21.226), -/ (12:16:06.943), -img (12:17:42.332), -{ (12:17:43.944), -width (12:17:46.547), -: (12:17:46.642), -50 (12:20:14.705), -% (12:20:15.067), -; (12:20:15.756), -: (12:24:02.925), -center (12:24:03.906), -; (12:24:04.138), -justify (12:24:05.215), -- (12:24:05.313), -content (12:24:06.156), -; (12:42:56.119)</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>91.2</v>
       </c>
@@ -5496,12 +4530,11 @@
           <t>-; (12:42:56.119), +" (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S82" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5549,7 +4582,6 @@
           <t>+" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +50px (00:00:00), +; (00:00:00), += (00:00:00), +chess (00:00:00), +const (00:00:00), +handelClick (00:00:00), +handelClick (00:00:00), +onclick (00:00:00), +this (00:00:00), -Chess (11:54:35.668), -50 (12:20:14.705), -% (12:20:15.067), -handleClick (12:33:15.189), -let (12:56:53.102)</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>98.8</v>
       </c>
@@ -5574,12 +4606,11 @@
           <t>-handleClick (12:33:15.189), -let (12:56:53.102), +const (00:00:00), +handelClick (00:00:00)</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S83" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5595,24 +4626,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5633,24 +4646,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5672,22 +4667,6 @@
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
       <c r="V86" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5709,22 +4688,6 @@
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5746,22 +4709,6 @@
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
       <c r="V88" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5783,22 +4730,6 @@
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5820,22 +4751,6 @@
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5857,22 +4772,6 @@
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5894,22 +4793,6 @@
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5931,22 +4814,6 @@
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5968,22 +4835,6 @@
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6005,22 +4856,6 @@
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6042,22 +4877,6 @@
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6079,22 +4898,6 @@
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6116,22 +4919,6 @@
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6153,22 +4940,6 @@
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6190,22 +4961,6 @@
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
           <t>LLM</t>
